--- a/mock-data/credit-master-data.xlsx
+++ b/mock-data/credit-master-data.xlsx
@@ -769,7 +769,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>INV-AC-5501</t>
+          <t>INV-GL-5501</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
@@ -797,7 +797,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>INV-AC-6602</t>
+          <t>INV-EK-6602</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
@@ -825,7 +825,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>INV-AC-6610</t>
+          <t>INV-EK-6610</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -853,7 +853,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>INV-IN-9901</t>
+          <t>INV-MT-9901</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">

--- a/mock-data/credit-master-data.xlsx
+++ b/mock-data/credit-master-data.xlsx
@@ -542,7 +542,7 @@
         <v>1000000</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>650000</v>
+        <v>30000</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
